--- a/tipo de atividade.xlsx
+++ b/tipo de atividade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.nave\OneDrive - Câmara Municipal de Lisboa\_UCT_DPAP - EQUIPA - 02 PRODUÇÃO\SELO ACESSIBILIDADE\Levantamento Av Liberdade  Julho 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71AE9BAE-8D98-42D7-A534-A3F1CB4D7021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB2A2BA-6B34-49BE-8BA6-E3E684059532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C9E527C-8BB1-4127-8A9B-D1DBD4509BED}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Comércio</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>Convencional</t>
+  </si>
+  <si>
+    <t>Café e Pastelarias</t>
+  </si>
+  <si>
+    <t>Gelatarias</t>
   </si>
 </sst>
 </file>
@@ -506,6 +512,9 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
@@ -513,6 +522,9 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>

--- a/tipo de atividade.xlsx
+++ b/tipo de atividade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.nave\OneDrive - Câmara Municipal de Lisboa\_UCT_DPAP - EQUIPA - 02 PRODUÇÃO\SELO ACESSIBILIDADE\Levantamento Av Liberdade  Julho 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB2A2BA-6B34-49BE-8BA6-E3E684059532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC2A7A9-A2CB-4B36-B8E4-FB0A8CB24DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C9E527C-8BB1-4127-8A9B-D1DBD4509BED}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Comércio</t>
   </si>
@@ -87,6 +87,24 @@
   </si>
   <si>
     <t>Gelatarias</t>
+  </si>
+  <si>
+    <t>Água Luz Gás e Comunicações</t>
+  </si>
+  <si>
+    <t>Escritórios</t>
+  </si>
+  <si>
+    <t>Institutos e Associações</t>
+  </si>
+  <si>
+    <t>Antiquário</t>
+  </si>
+  <si>
+    <t>Tecnologia e Equipamentos</t>
+  </si>
+  <si>
+    <t>Mobiliário</t>
   </si>
 </sst>
 </file>
@@ -467,10 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E68A811-C117-410F-9AE3-9E64370120DC}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="31.28515625" customWidth="1"/>
   </cols>
@@ -531,8 +549,32 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
       <c r="C6" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
